--- a/SMC_Scalper_Results.xlsx
+++ b/SMC_Scalper_Results.xlsx
@@ -659,7 +659,7 @@
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
@@ -680,7 +680,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Pips and profit are net of spread, slippage and commission. Times are UTC.</t>
+          <t>Pips and profit are net of spread, slippage and commission, and cover the WHOLE trade including partial take-profits -- final_exit_price is only where the last portion closed. Times are UTC.</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="I4" s="11" t="inlineStr">
         <is>
-          <t>exit_price</t>
+          <t>final_exit_price</t>
         </is>
       </c>
       <c r="J4" s="11" t="inlineStr">
@@ -875,7 +875,7 @@
         <v>1.869</v>
       </c>
       <c r="J6" s="15" t="n">
-        <v>-21.4</v>
+        <v>-22.1</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>-2042.16</v>
@@ -1009,7 +1009,7 @@
         <v>1.60116</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>-7.7</v>
+        <v>2</v>
       </c>
       <c r="K8" s="16" t="n">
         <v>219.21</v>
@@ -1143,7 +1143,7 @@
         <v>1.37545</v>
       </c>
       <c r="J10" s="15" t="n">
-        <v>-10.8</v>
+        <v>-1.7</v>
       </c>
       <c r="K10" s="16" t="n">
         <v>-310.64</v>
@@ -1210,7 +1210,7 @@
         <v>0.71288</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>-12.5</v>
+        <v>-13.2</v>
       </c>
       <c r="K11" s="16" t="n">
         <v>-2042.89</v>
@@ -1344,7 +1344,7 @@
         <v>1.88434</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>-24.8</v>
+        <v>-25.5</v>
       </c>
       <c r="K13" s="16" t="n">
         <v>-1892.09</v>
@@ -1478,7 +1478,7 @@
         <v>1.15845</v>
       </c>
       <c r="J15" s="15" t="n">
-        <v>19.9</v>
+        <v>15.3</v>
       </c>
       <c r="K15" s="16" t="n">
         <v>2238.94</v>
@@ -1545,7 +1545,7 @@
         <v>0.81021</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>29.3</v>
+        <v>20.8</v>
       </c>
       <c r="K16" s="16" t="n">
         <v>2126.18</v>
@@ -1612,7 +1612,7 @@
         <v>1.16072</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>0.3</v>
+        <v>4.7</v>
       </c>
       <c r="K17" s="16" t="n">
         <v>856.04</v>
@@ -1679,7 +1679,7 @@
         <v>4511.84229</v>
       </c>
       <c r="J18" s="15" t="n">
-        <v>-185.4</v>
+        <v>-186.1</v>
       </c>
       <c r="K18" s="16" t="n">
         <v>-330.15</v>
@@ -1746,7 +1746,7 @@
         <v>113.53612</v>
       </c>
       <c r="J19" s="15" t="n">
-        <v>0.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="K19" s="16" t="n">
         <v>1082.34</v>
@@ -1880,7 +1880,7 @@
         <v>1.34266</v>
       </c>
       <c r="J21" s="15" t="n">
-        <v>0.4</v>
+        <v>-0.3</v>
       </c>
       <c r="K21" s="16" t="n">
         <v>-59.8</v>
@@ -1947,7 +1947,7 @@
         <v>1.60305</v>
       </c>
       <c r="J22" s="15" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="K22" s="16" t="n">
         <v>2055.28</v>
@@ -2014,7 +2014,7 @@
         <v>1.16204</v>
       </c>
       <c r="J23" s="15" t="n">
-        <v>-14.4</v>
+        <v>-15.1</v>
       </c>
       <c r="K23" s="16" t="n">
         <v>-1990.72</v>
@@ -2081,7 +2081,7 @@
         <v>0.71692</v>
       </c>
       <c r="J24" s="15" t="n">
-        <v>-8.199999999999999</v>
+        <v>-8.9</v>
       </c>
       <c r="K24" s="16" t="n">
         <v>-1994.07</v>
@@ -2148,7 +2148,7 @@
         <v>1.1646</v>
       </c>
       <c r="J25" s="15" t="n">
-        <v>-8.4</v>
+        <v>-9.1</v>
       </c>
       <c r="K25" s="16" t="n">
         <v>-2033.55</v>
@@ -2282,7 +2282,7 @@
         <v>0.78553</v>
       </c>
       <c r="J27" s="15" t="n">
-        <v>0.3</v>
+        <v>4.2</v>
       </c>
       <c r="K27" s="16" t="n">
         <v>724.55</v>
@@ -2349,7 +2349,7 @@
         <v>1.16499</v>
       </c>
       <c r="J28" s="15" t="n">
-        <v>-9</v>
+        <v>-1.4</v>
       </c>
       <c r="K28" s="16" t="n">
         <v>-282.49</v>
@@ -2416,7 +2416,7 @@
         <v>214.27813</v>
       </c>
       <c r="J29" s="15" t="n">
-        <v>0.7</v>
+        <v>6.8</v>
       </c>
       <c r="K29" s="16" t="n">
         <v>688.8</v>
@@ -2483,7 +2483,7 @@
         <v>1.34282</v>
       </c>
       <c r="J30" s="15" t="n">
-        <v>-15.1</v>
+        <v>-1.8</v>
       </c>
       <c r="K30" s="16" t="n">
         <v>-206.04</v>
@@ -2550,7 +2550,7 @@
         <v>185.59857</v>
       </c>
       <c r="J31" s="15" t="n">
-        <v>0.5</v>
+        <v>5.7</v>
       </c>
       <c r="K31" s="16" t="n">
         <v>742.7</v>
@@ -2617,7 +2617,7 @@
         <v>202.63411</v>
       </c>
       <c r="J32" s="15" t="n">
-        <v>-28.1</v>
+        <v>-2.3</v>
       </c>
       <c r="K32" s="16" t="n">
         <v>-144.12</v>
@@ -2684,7 +2684,7 @@
         <v>1.38287</v>
       </c>
       <c r="J33" s="15" t="n">
-        <v>-4.9</v>
+        <v>-5.6</v>
       </c>
       <c r="K33" s="16" t="n">
         <v>-763.39</v>
@@ -2751,7 +2751,7 @@
         <v>1.33938</v>
       </c>
       <c r="J34" s="15" t="n">
-        <v>-12.3</v>
+        <v>-13</v>
       </c>
       <c r="K34" s="16" t="n">
         <v>-1860.02</v>
@@ -2818,7 +2818,7 @@
         <v>1.38533</v>
       </c>
       <c r="J35" s="15" t="n">
-        <v>-11.7</v>
+        <v>-12.4</v>
       </c>
       <c r="K35" s="16" t="n">
         <v>-1827.24</v>
@@ -2885,7 +2885,7 @@
         <v>4407.70171</v>
       </c>
       <c r="J36" s="15" t="n">
-        <v>-187.2</v>
+        <v>-187.9</v>
       </c>
       <c r="K36" s="16" t="n">
         <v>-291.47</v>
@@ -2952,7 +2952,7 @@
         <v>1.16489</v>
       </c>
       <c r="J37" s="15" t="n">
-        <v>-6.8</v>
+        <v>-7.5</v>
       </c>
       <c r="K37" s="16" t="n">
         <v>-1878.6</v>
@@ -3019,7 +3019,7 @@
         <v>1.62341</v>
       </c>
       <c r="J38" s="15" t="n">
-        <v>14.4</v>
+        <v>13.7</v>
       </c>
       <c r="K38" s="16" t="n">
         <v>807.36</v>
@@ -3086,7 +3086,7 @@
         <v>159.83714</v>
       </c>
       <c r="J39" s="15" t="n">
-        <v>12.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="K39" s="16" t="n">
         <v>2413.62</v>
@@ -3153,7 +3153,7 @@
         <v>215.43929</v>
       </c>
       <c r="J40" s="15" t="n">
-        <v>23.6</v>
+        <v>17.5</v>
       </c>
       <c r="K40" s="16" t="n">
         <v>1868.53</v>
@@ -3354,7 +3354,7 @@
         <v>1.86015</v>
       </c>
       <c r="J43" s="15" t="n">
-        <v>-23.9</v>
+        <v>-24.6</v>
       </c>
       <c r="K43" s="16" t="n">
         <v>-1709.79</v>
@@ -3421,7 +3421,7 @@
         <v>1.89318</v>
       </c>
       <c r="J44" s="15" t="n">
-        <v>27.2</v>
+        <v>29.6</v>
       </c>
       <c r="K44" s="16" t="n">
         <v>1468.62</v>
@@ -3488,7 +3488,7 @@
         <v>0.58111</v>
       </c>
       <c r="J45" s="15" t="n">
-        <v>8.300000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="K45" s="16" t="n">
         <v>827.87</v>
@@ -3555,7 +3555,7 @@
         <v>2.29383</v>
       </c>
       <c r="J46" s="15" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.5</v>
       </c>
       <c r="K46" s="16" t="n">
         <v>-450.33</v>
@@ -3622,7 +3622,7 @@
         <v>1.33791</v>
       </c>
       <c r="J47" s="15" t="n">
-        <v>-10.3</v>
+        <v>-11</v>
       </c>
       <c r="K47" s="16" t="n">
         <v>-1797.15</v>
@@ -3689,7 +3689,7 @@
         <v>185.278</v>
       </c>
       <c r="J48" s="15" t="n">
-        <v>0.5</v>
+        <v>8.4</v>
       </c>
       <c r="K48" s="16" t="n">
         <v>908.84</v>
@@ -3744,7 +3744,7 @@
         <v>17.9036</v>
       </c>
       <c r="F49" s="14" t="n">
-        <v>1.3383</v>
+        <v>1.33831</v>
       </c>
       <c r="G49" s="14" t="n">
         <v>1.33739</v>
@@ -3756,7 +3756,7 @@
         <v>1.33737</v>
       </c>
       <c r="J49" s="15" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10</v>
       </c>
       <c r="K49" s="16" t="n">
         <v>-1793.23</v>
@@ -3823,7 +3823,7 @@
         <v>1.15391</v>
       </c>
       <c r="J50" s="15" t="n">
-        <v>-7.9</v>
+        <v>-8.6</v>
       </c>
       <c r="K50" s="16" t="n">
         <v>-1783.68</v>
@@ -3890,7 +3890,7 @@
         <v>1.15216</v>
       </c>
       <c r="J51" s="15" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="K51" s="16" t="n">
         <v>-1769.32</v>
@@ -3957,7 +3957,7 @@
         <v>213.99725</v>
       </c>
       <c r="J52" s="15" t="n">
-        <v>56.9</v>
+        <v>41.1</v>
       </c>
       <c r="K52" s="16" t="n">
         <v>2425.98</v>
@@ -4024,7 +4024,7 @@
         <v>0.70391</v>
       </c>
       <c r="J53" s="15" t="n">
-        <v>0.2</v>
+        <v>2.7</v>
       </c>
       <c r="K53" s="16" t="n">
         <v>504.19</v>
@@ -4091,7 +4091,7 @@
         <v>0.79654</v>
       </c>
       <c r="J54" s="15" t="n">
-        <v>-3.5</v>
+        <v>-4.2</v>
       </c>
       <c r="K54" s="16" t="n">
         <v>-447.43</v>
@@ -4158,7 +4158,7 @@
         <v>0.70491</v>
       </c>
       <c r="J55" s="15" t="n">
-        <v>10.8</v>
+        <v>11.9</v>
       </c>
       <c r="K55" s="16" t="n">
         <v>1137.13</v>
@@ -4225,7 +4225,7 @@
         <v>1.16029</v>
       </c>
       <c r="J56" s="15" t="n">
-        <v>-8.9</v>
+        <v>-9.6</v>
       </c>
       <c r="K56" s="16" t="n">
         <v>-1763.32</v>
@@ -4292,7 +4292,7 @@
         <v>214.93626</v>
       </c>
       <c r="J57" s="15" t="n">
-        <v>-16</v>
+        <v>-1</v>
       </c>
       <c r="K57" s="16" t="n">
         <v>-103.41</v>
@@ -4426,7 +4426,7 @@
         <v>1.87861</v>
       </c>
       <c r="J59" s="15" t="n">
-        <v>0.7</v>
+        <v>-0</v>
       </c>
       <c r="K59" s="16" t="n">
         <v>-4.87</v>
@@ -4493,7 +4493,7 @@
         <v>0.79297</v>
       </c>
       <c r="J60" s="15" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="K60" s="16" t="n">
         <v>1133.7</v>
@@ -4560,7 +4560,7 @@
         <v>4331.45</v>
       </c>
       <c r="J61" s="15" t="n">
-        <v>-45.3</v>
+        <v>-46</v>
       </c>
       <c r="K61" s="16" t="n">
         <v>-39.82</v>
@@ -4627,7 +4627,7 @@
         <v>1.87671</v>
       </c>
       <c r="J62" s="15" t="n">
-        <v>-19.2</v>
+        <v>-19.9</v>
       </c>
       <c r="K62" s="16" t="n">
         <v>-1673.4</v>
@@ -4761,7 +4761,7 @@
         <v>1.40318</v>
       </c>
       <c r="J64" s="15" t="n">
-        <v>24.8</v>
+        <v>18</v>
       </c>
       <c r="K64" s="16" t="n">
         <v>2370.27</v>
@@ -4962,7 +4962,7 @@
         <v>0.80748</v>
       </c>
       <c r="J67" s="15" t="n">
-        <v>-10.7</v>
+        <v>-11.4</v>
       </c>
       <c r="K67" s="16" t="n">
         <v>-1562.86</v>
@@ -5029,7 +5029,7 @@
         <v>1.32208</v>
       </c>
       <c r="J68" s="15" t="n">
-        <v>-17.8</v>
+        <v>-18.5</v>
       </c>
       <c r="K68" s="16" t="n">
         <v>-1545.57</v>
@@ -5084,7 +5084,7 @@
         <v>7.2472</v>
       </c>
       <c r="F69" s="14" t="n">
-        <v>1.87632</v>
+        <v>1.87631</v>
       </c>
       <c r="G69" s="14" t="n">
         <v>1.87822</v>
@@ -5096,7 +5096,7 @@
         <v>1.87624</v>
       </c>
       <c r="J69" s="15" t="n">
-        <v>0.8</v>
+        <v>0.1</v>
       </c>
       <c r="K69" s="16" t="n">
         <v>3.69</v>
@@ -5163,7 +5163,7 @@
         <v>0.80727</v>
       </c>
       <c r="J70" s="15" t="n">
-        <v>-15.8</v>
+        <v>-16.5</v>
       </c>
       <c r="K70" s="16" t="n">
         <v>-1489.53</v>
@@ -5230,7 +5230,7 @@
         <v>1.32267</v>
       </c>
       <c r="J71" s="15" t="n">
-        <v>-12.8</v>
+        <v>-13.5</v>
       </c>
       <c r="K71" s="16" t="n">
         <v>-1476.9</v>
@@ -5297,7 +5297,7 @@
         <v>2.0068</v>
       </c>
       <c r="J72" s="15" t="n">
-        <v>-24.7</v>
+        <v>-25.4</v>
       </c>
       <c r="K72" s="16" t="n">
         <v>-1398.46</v>
@@ -5364,7 +5364,7 @@
         <v>1.13661</v>
       </c>
       <c r="J73" s="15" t="n">
-        <v>-6.6</v>
+        <v>-7.3</v>
       </c>
       <c r="K73" s="16" t="n">
         <v>-1506.87</v>
@@ -5431,7 +5431,7 @@
         <v>0.98047</v>
       </c>
       <c r="J74" s="15" t="n">
-        <v>-16.7</v>
+        <v>-17.4</v>
       </c>
       <c r="K74" s="16" t="n">
         <v>-1361.14</v>
@@ -5498,7 +5498,7 @@
         <v>1.64378</v>
       </c>
       <c r="J75" s="15" t="n">
-        <v>-30.7</v>
+        <v>-31.4</v>
       </c>
       <c r="K75" s="16" t="n">
         <v>-1289.96</v>
@@ -5565,7 +5565,7 @@
         <v>1.90842</v>
       </c>
       <c r="J76" s="15" t="n">
-        <v>-12.6</v>
+        <v>-13.3</v>
       </c>
       <c r="K76" s="16" t="n">
         <v>-534.91</v>
@@ -5632,7 +5632,7 @@
         <v>0.55929</v>
       </c>
       <c r="J77" s="15" t="n">
-        <v>0.8</v>
+        <v>0</v>
       </c>
       <c r="K77" s="16" t="n">
         <v>4.1</v>
@@ -5687,7 +5687,7 @@
         <v>7.0549</v>
       </c>
       <c r="F78" s="14" t="n">
-        <v>1.06732</v>
+        <v>1.06733</v>
       </c>
       <c r="G78" s="14" t="n">
         <v>1.06906</v>
@@ -5699,7 +5699,7 @@
         <v>1.06908</v>
       </c>
       <c r="J78" s="15" t="n">
-        <v>-17.6</v>
+        <v>-18.3</v>
       </c>
       <c r="K78" s="16" t="n">
         <v>-1290.68</v>
@@ -5766,7 +5766,7 @@
         <v>1.32211</v>
       </c>
       <c r="J79" s="15" t="n">
-        <v>-13.2</v>
+        <v>-13.9</v>
       </c>
       <c r="K79" s="16" t="n">
         <v>-1284.61</v>
@@ -5833,7 +5833,7 @@
         <v>0.92242</v>
       </c>
       <c r="J80" s="15" t="n">
-        <v>-0.5</v>
+        <v>-1.2</v>
       </c>
       <c r="K80" s="16" t="n">
         <v>-103.34</v>
@@ -5900,7 +5900,7 @@
         <v>1.88213</v>
       </c>
       <c r="J81" s="15" t="n">
-        <v>-3.7</v>
+        <v>-4.4</v>
       </c>
       <c r="K81" s="16" t="n">
         <v>-192.77</v>
@@ -5967,7 +5967,7 @@
         <v>0.86107</v>
       </c>
       <c r="J82" s="15" t="n">
-        <v>-1.5</v>
+        <v>-2.1</v>
       </c>
       <c r="K82" s="16" t="n">
         <v>-188.44</v>
@@ -6034,7 +6034,7 @@
         <v>0.68873</v>
       </c>
       <c r="J83" s="15" t="n">
-        <v>-8.300000000000001</v>
+        <v>-9</v>
       </c>
       <c r="K83" s="16" t="n">
         <v>-1295.48</v>
@@ -6168,7 +6168,7 @@
         <v>2.34045</v>
       </c>
       <c r="J85" s="15" t="n">
-        <v>62.9</v>
+        <v>41.4</v>
       </c>
       <c r="K85" s="16" t="n">
         <v>1414.74</v>
@@ -6235,7 +6235,7 @@
         <v>0.56713</v>
       </c>
       <c r="J86" s="15" t="n">
-        <v>-6.9</v>
+        <v>-7.6</v>
       </c>
       <c r="K86" s="16" t="n">
         <v>-396.48</v>
@@ -6369,7 +6369,7 @@
         <v>1.14163</v>
       </c>
       <c r="J88" s="15" t="n">
-        <v>-11</v>
+        <v>-11.7</v>
       </c>
       <c r="K88" s="16" t="n">
         <v>-1247.32</v>
@@ -6436,7 +6436,7 @@
         <v>1.62154</v>
       </c>
       <c r="J89" s="15" t="n">
-        <v>0.7</v>
+        <v>6.6</v>
       </c>
       <c r="K89" s="16" t="n">
         <v>399.17</v>
@@ -6497,13 +6497,13 @@
         <v>113.73262</v>
       </c>
       <c r="H90" s="14" t="n">
-        <v>113.14813</v>
+        <v>113.14812</v>
       </c>
       <c r="I90" s="14" t="n">
         <v>113.578</v>
       </c>
       <c r="J90" s="15" t="n">
-        <v>-1.3</v>
+        <v>6.1</v>
       </c>
       <c r="K90" s="16" t="n">
         <v>411.05</v>
@@ -6570,7 +6570,7 @@
         <v>0.69242</v>
       </c>
       <c r="J91" s="15" t="n">
-        <v>-8</v>
+        <v>-8.699999999999999</v>
       </c>
       <c r="K91" s="16" t="n">
         <v>-1308.29</v>
@@ -6637,7 +6637,7 @@
         <v>1.33661</v>
       </c>
       <c r="J92" s="15" t="n">
-        <v>25.2</v>
+        <v>18.3</v>
       </c>
       <c r="K92" s="16" t="n">
         <v>1522.62</v>
@@ -6692,7 +6692,7 @@
         <v>5.6335</v>
       </c>
       <c r="F93" s="14" t="n">
-        <v>1.897</v>
+        <v>1.89701</v>
       </c>
       <c r="G93" s="14" t="n">
         <v>1.89497</v>
@@ -6704,7 +6704,7 @@
         <v>1.90088</v>
       </c>
       <c r="J93" s="15" t="n">
-        <v>38.8</v>
+        <v>31.2</v>
       </c>
       <c r="K93" s="16" t="n">
         <v>1757.18</v>
@@ -6771,7 +6771,7 @@
         <v>1.33751</v>
       </c>
       <c r="J94" s="15" t="n">
-        <v>-17.4</v>
+        <v>-18.1</v>
       </c>
       <c r="K94" s="16" t="n">
         <v>-1243.82</v>
@@ -6838,7 +6838,7 @@
         <v>1.42015</v>
       </c>
       <c r="J95" s="15" t="n">
-        <v>-11.9</v>
+        <v>-12.6</v>
       </c>
       <c r="K95" s="16" t="n">
         <v>-1220.56</v>
@@ -6972,7 +6972,7 @@
         <v>1.14308</v>
       </c>
       <c r="J97" s="15" t="n">
-        <v>0.1</v>
+        <v>2</v>
       </c>
       <c r="K97" s="16" t="n">
         <v>324.62</v>
@@ -7039,7 +7039,7 @@
         <v>1.14123</v>
       </c>
       <c r="J98" s="15" t="n">
-        <v>0.5</v>
+        <v>6.8</v>
       </c>
       <c r="K98" s="16" t="n">
         <v>506.94</v>
@@ -7106,7 +7106,7 @@
         <v>217.37325</v>
       </c>
       <c r="J99" s="15" t="n">
-        <v>51</v>
+        <v>40.3</v>
       </c>
       <c r="K99" s="16" t="n">
         <v>1745.94</v>
@@ -7173,7 +7173,7 @@
         <v>1.08266</v>
       </c>
       <c r="J100" s="15" t="n">
-        <v>33.1</v>
+        <v>24.2</v>
       </c>
       <c r="K100" s="16" t="n">
         <v>2001.77</v>
@@ -7240,7 +7240,7 @@
         <v>1.14142</v>
       </c>
       <c r="J101" s="15" t="n">
-        <v>-13.1</v>
+        <v>-13.8</v>
       </c>
       <c r="K101" s="16" t="n">
         <v>-1314.28</v>
@@ -7307,7 +7307,7 @@
         <v>0.69346</v>
       </c>
       <c r="J102" s="15" t="n">
-        <v>-11.2</v>
+        <v>-11.9</v>
       </c>
       <c r="K102" s="16" t="n">
         <v>-742.4299999999999</v>
@@ -7374,7 +7374,7 @@
         <v>112.607</v>
       </c>
       <c r="J103" s="15" t="n">
-        <v>11.5</v>
+        <v>17</v>
       </c>
       <c r="K103" s="16" t="n">
         <v>806.59</v>
@@ -7441,7 +7441,7 @@
         <v>1.64694</v>
       </c>
       <c r="J104" s="15" t="n">
-        <v>0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="K104" s="16" t="n">
         <v>-3.88</v>
@@ -7508,7 +7508,7 @@
         <v>185.595</v>
       </c>
       <c r="J105" s="15" t="n">
-        <v>19.6</v>
+        <v>24.1</v>
       </c>
       <c r="K105" s="16" t="n">
         <v>1341.08</v>
@@ -7575,7 +7575,7 @@
         <v>1.08135</v>
       </c>
       <c r="J106" s="15" t="n">
-        <v>-16</v>
+        <v>-16.7</v>
       </c>
       <c r="K106" s="16" t="n">
         <v>-1276.03</v>
@@ -7709,7 +7709,7 @@
         <v>1.14292</v>
       </c>
       <c r="J108" s="15" t="n">
-        <v>0.3</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K108" s="16" t="n">
         <v>1042.82</v>
@@ -7776,7 +7776,7 @@
         <v>1.41629</v>
       </c>
       <c r="J109" s="15" t="n">
-        <v>-14.5</v>
+        <v>-15.2</v>
       </c>
       <c r="K109" s="16" t="n">
         <v>-1282.28</v>
@@ -7843,7 +7843,7 @@
         <v>1.3405</v>
       </c>
       <c r="J110" s="15" t="n">
-        <v>16.6</v>
+        <v>12</v>
       </c>
       <c r="K110" s="16" t="n">
         <v>1410.77</v>
@@ -7910,7 +7910,7 @@
         <v>201.308</v>
       </c>
       <c r="J111" s="15" t="n">
-        <v>-7.6</v>
+        <v>4.2</v>
       </c>
       <c r="K111" s="16" t="n">
         <v>241.64</v>
@@ -8044,7 +8044,7 @@
         <v>217.689</v>
       </c>
       <c r="J113" s="15" t="n">
-        <v>13.2</v>
+        <v>14.2</v>
       </c>
       <c r="K113" s="16" t="n">
         <v>886.47</v>
@@ -8111,7 +8111,7 @@
         <v>1.93004</v>
       </c>
       <c r="J114" s="15" t="n">
-        <v>-29</v>
+        <v>-29.7</v>
       </c>
       <c r="K114" s="16" t="n">
         <v>-1184.67</v>
@@ -8178,7 +8178,7 @@
         <v>1.34078</v>
       </c>
       <c r="J115" s="15" t="n">
-        <v>-9.9</v>
+        <v>-10.6</v>
       </c>
       <c r="K115" s="16" t="n">
         <v>-1283.16</v>
@@ -8245,7 +8245,7 @@
         <v>0.57577</v>
       </c>
       <c r="J116" s="15" t="n">
-        <v>-10.6</v>
+        <v>-11.2</v>
       </c>
       <c r="K116" s="16" t="n">
         <v>-970.41</v>
@@ -8312,7 +8312,7 @@
         <v>0.80985</v>
       </c>
       <c r="J117" s="15" t="n">
-        <v>-11.6</v>
+        <v>-12.3</v>
       </c>
       <c r="K117" s="16" t="n">
         <v>-1205.99</v>
@@ -8379,7 +8379,7 @@
         <v>0.57681</v>
       </c>
       <c r="J118" s="15" t="n">
-        <v>4</v>
+        <v>7.5</v>
       </c>
       <c r="K118" s="16" t="n">
         <v>599.14</v>
@@ -8446,7 +8446,7 @@
         <v>162.40268</v>
       </c>
       <c r="J119" s="15" t="n">
-        <v>25.1</v>
+        <v>18.9</v>
       </c>
       <c r="K119" s="16" t="n">
         <v>1530.84</v>
@@ -8513,7 +8513,7 @@
         <v>184.768</v>
       </c>
       <c r="J120" s="15" t="n">
-        <v>24.3</v>
+        <v>16.6</v>
       </c>
       <c r="K120" s="16" t="n">
         <v>1715</v>
@@ -8580,7 +8580,7 @@
         <v>1.8849</v>
       </c>
       <c r="J121" s="15" t="n">
-        <v>-22.6</v>
+        <v>-23.3</v>
       </c>
       <c r="K121" s="16" t="n">
         <v>-1204.99</v>
@@ -8647,7 +8647,7 @@
         <v>1.40299</v>
       </c>
       <c r="J122" s="15" t="n">
-        <v>31.5</v>
+        <v>22.4</v>
       </c>
       <c r="K122" s="16" t="n">
         <v>1468.73</v>
@@ -8781,7 +8781,7 @@
         <v>1.14549</v>
       </c>
       <c r="J124" s="15" t="n">
-        <v>-12.5</v>
+        <v>-13.2</v>
       </c>
       <c r="K124" s="16" t="n">
         <v>-1223.15</v>
@@ -8848,7 +8848,7 @@
         <v>162.32562</v>
       </c>
       <c r="J125" s="15" t="n">
-        <v>0.2</v>
+        <v>3.6</v>
       </c>
       <c r="K125" s="16" t="n">
         <v>483.68</v>
@@ -8915,7 +8915,7 @@
         <v>1.40182</v>
       </c>
       <c r="J126" s="15" t="n">
-        <v>9.199999999999999</v>
+        <v>12.4</v>
       </c>
       <c r="K126" s="16" t="n">
         <v>994.5700000000001</v>
@@ -8982,7 +8982,7 @@
         <v>0.8072</v>
       </c>
       <c r="J127" s="15" t="n">
-        <v>-3.3</v>
+        <v>-3.9</v>
       </c>
       <c r="K127" s="16" t="n">
         <v>-475.13</v>
@@ -9049,7 +9049,7 @@
         <v>1.1433</v>
       </c>
       <c r="J128" s="15" t="n">
-        <v>-8.5</v>
+        <v>-9.199999999999999</v>
       </c>
       <c r="K128" s="16" t="n">
         <v>-1258.98</v>
@@ -9116,7 +9116,7 @@
         <v>218.17032</v>
       </c>
       <c r="J129" s="15" t="n">
-        <v>43.3</v>
+        <v>31.1</v>
       </c>
       <c r="K129" s="16" t="n">
         <v>1610.55</v>
@@ -9183,7 +9183,7 @@
         <v>0.69946</v>
       </c>
       <c r="J130" s="15" t="n">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="K130" s="16" t="n">
         <v>803.5599999999999</v>
@@ -9250,7 +9250,7 @@
         <v>1.34195</v>
       </c>
       <c r="J131" s="15" t="n">
-        <v>25.1</v>
+        <v>16.9</v>
       </c>
       <c r="K131" s="16" t="n">
         <v>1597.37</v>
@@ -9317,7 +9317,7 @@
         <v>0.69887</v>
       </c>
       <c r="J132" s="15" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10</v>
       </c>
       <c r="K132" s="16" t="n">
         <v>-1307.83</v>
@@ -9384,7 +9384,7 @@
         <v>218.13512</v>
       </c>
       <c r="J133" s="15" t="n">
-        <v>1.3</v>
+        <v>14.4</v>
       </c>
       <c r="K133" s="16" t="n">
         <v>562.8</v>
@@ -9451,7 +9451,7 @@
         <v>0.81158</v>
       </c>
       <c r="J134" s="15" t="n">
-        <v>-9.800000000000001</v>
+        <v>-10.5</v>
       </c>
       <c r="K134" s="16" t="n">
         <v>-1310.14</v>
@@ -9518,7 +9518,7 @@
         <v>200.443</v>
       </c>
       <c r="J135" s="15" t="n">
-        <v>25.9</v>
+        <v>23.1</v>
       </c>
       <c r="K135" s="16" t="n">
         <v>1107.8</v>
@@ -9585,7 +9585,7 @@
         <v>0.69958</v>
       </c>
       <c r="J136" s="15" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="K136" s="16" t="n">
         <v>130.84</v>
@@ -9719,7 +9719,7 @@
         <v>1.40824</v>
       </c>
       <c r="J138" s="15" t="n">
-        <v>0.3</v>
+        <v>3.3</v>
       </c>
       <c r="K138" s="16" t="n">
         <v>375.6</v>
@@ -9853,7 +9853,7 @@
         <v>0.85408</v>
       </c>
       <c r="J140" s="15" t="n">
-        <v>-1.4</v>
+        <v>-2.1</v>
       </c>
       <c r="K140" s="16" t="n">
         <v>-180.4</v>
@@ -9987,7 +9987,7 @@
         <v>200.11254</v>
       </c>
       <c r="J142" s="15" t="n">
-        <v>50.1</v>
+        <v>36.6</v>
       </c>
       <c r="K142" s="16" t="n">
         <v>1507.06</v>
@@ -10109,7 +10109,7 @@
         <v>6.8532</v>
       </c>
       <c r="F144" s="14" t="n">
-        <v>1.87738</v>
+        <v>1.87739</v>
       </c>
       <c r="G144" s="14" t="n">
         <v>1.87576</v>
@@ -10121,7 +10121,7 @@
         <v>1.87574</v>
       </c>
       <c r="J144" s="15" t="n">
-        <v>-16.5</v>
+        <v>-17.2</v>
       </c>
       <c r="K144" s="16" t="n">
         <v>-1176.55</v>
@@ -10322,7 +10322,7 @@
         <v>0.81852</v>
       </c>
       <c r="J147" s="15" t="n">
-        <v>-10.4</v>
+        <v>-11.1</v>
       </c>
       <c r="K147" s="16" t="n">
         <v>-1187.45</v>
@@ -10377,7 +10377,7 @@
         <v>9.020899999999999</v>
       </c>
       <c r="F148" s="14" t="n">
-        <v>1.40948</v>
+        <v>1.40949</v>
       </c>
       <c r="G148" s="14" t="n">
         <v>1.40835</v>
@@ -10389,7 +10389,7 @@
         <v>1.40952</v>
       </c>
       <c r="J148" s="15" t="n">
-        <v>0.4</v>
+        <v>4</v>
       </c>
       <c r="K148" s="16" t="n">
         <v>361.65</v>
@@ -10456,7 +10456,7 @@
         <v>2.30175</v>
       </c>
       <c r="J149" s="15" t="n">
-        <v>-28.5</v>
+        <v>-29.2</v>
       </c>
       <c r="K149" s="16" t="n">
         <v>-1088.38</v>
@@ -10523,7 +10523,7 @@
         <v>186.634</v>
       </c>
       <c r="J150" s="15" t="n">
-        <v>22.1</v>
+        <v>19.8</v>
       </c>
       <c r="K150" s="16" t="n">
         <v>1140.12</v>
@@ -10791,7 +10791,7 @@
         <v>1.4035</v>
       </c>
       <c r="J154" s="15" t="n">
-        <v>-10.6</v>
+        <v>-11.3</v>
       </c>
       <c r="K154" s="16" t="n">
         <v>-1093.49</v>
@@ -10858,7 +10858,7 @@
         <v>1.08226</v>
       </c>
       <c r="J155" s="15" t="n">
-        <v>51.6</v>
+        <v>33.8</v>
       </c>
       <c r="K155" s="16" t="n">
         <v>1746.29</v>
@@ -10925,7 +10925,7 @@
         <v>0.80798</v>
       </c>
       <c r="J156" s="15" t="n">
-        <v>-9.300000000000001</v>
+        <v>-10</v>
       </c>
       <c r="K156" s="16" t="n">
         <v>-1082.09</v>
@@ -10992,7 +10992,7 @@
         <v>111.55511</v>
       </c>
       <c r="J157" s="15" t="n">
-        <v>82.59999999999999</v>
+        <v>70.7</v>
       </c>
       <c r="K157" s="16" t="n">
         <v>1737.13</v>
@@ -11059,7 +11059,7 @@
         <v>93.30568</v>
       </c>
       <c r="J158" s="15" t="n">
-        <v>59.2</v>
+        <v>62.6</v>
       </c>
       <c r="K158" s="16" t="n">
         <v>1981.79</v>
@@ -11126,7 +11126,7 @@
         <v>2.29233</v>
       </c>
       <c r="J159" s="15" t="n">
-        <v>-38.7</v>
+        <v>-39.4</v>
       </c>
       <c r="K159" s="16" t="n">
         <v>-1107.47</v>
@@ -11193,7 +11193,7 @@
         <v>113.227</v>
       </c>
       <c r="J160" s="15" t="n">
-        <v>77</v>
+        <v>61.6</v>
       </c>
       <c r="K160" s="16" t="n">
         <v>1365.74</v>
@@ -11260,7 +11260,7 @@
         <v>1.95656</v>
       </c>
       <c r="J161" s="15" t="n">
-        <v>24.7</v>
+        <v>21.4</v>
       </c>
       <c r="K161" s="16" t="n">
         <v>870.14</v>
@@ -11327,7 +11327,7 @@
         <v>1.64038</v>
       </c>
       <c r="J162" s="15" t="n">
-        <v>22</v>
+        <v>22.2</v>
       </c>
       <c r="K162" s="16" t="n">
         <v>844.17</v>
@@ -11394,7 +11394,7 @@
         <v>156.54596</v>
       </c>
       <c r="J163" s="15" t="n">
-        <v>31</v>
+        <v>30.2</v>
       </c>
       <c r="K163" s="16" t="n">
         <v>1591.34</v>
@@ -11461,7 +11461,7 @@
         <v>210.7495</v>
       </c>
       <c r="J164" s="15" t="n">
-        <v>38.6</v>
+        <v>32.3</v>
       </c>
       <c r="K164" s="16" t="n">
         <v>1411.45</v>
@@ -11528,7 +11528,7 @@
         <v>1.4046</v>
       </c>
       <c r="J165" s="15" t="n">
-        <v>-15</v>
+        <v>-15.7</v>
       </c>
       <c r="K165" s="16" t="n">
         <v>-1150.67</v>
@@ -11595,7 +11595,7 @@
         <v>1.15192</v>
       </c>
       <c r="J166" s="15" t="n">
-        <v>-9.9</v>
+        <v>-10.6</v>
       </c>
       <c r="K166" s="16" t="n">
         <v>-1211.62</v>
@@ -11863,7 +11863,7 @@
         <v>4079.74</v>
       </c>
       <c r="J170" s="15" t="n">
-        <v>131.7</v>
+        <v>165.5</v>
       </c>
       <c r="K170" s="16" t="n">
         <v>133.31</v>
@@ -11997,7 +11997,7 @@
         <v>1.34613</v>
       </c>
       <c r="J172" s="15" t="n">
-        <v>-9.199999999999999</v>
+        <v>-9.9</v>
       </c>
       <c r="K172" s="16" t="n">
         <v>-1131.2</v>
@@ -12131,7 +12131,7 @@
         <v>1.96105</v>
       </c>
       <c r="J174" s="15" t="n">
-        <v>-29.5</v>
+        <v>-30.2</v>
       </c>
       <c r="K174" s="16" t="n">
         <v>-1043.27</v>
@@ -12332,7 +12332,7 @@
         <v>92.53914</v>
       </c>
       <c r="J177" s="15" t="n">
-        <v>37.6</v>
+        <v>24.3</v>
       </c>
       <c r="K177" s="16" t="n">
         <v>1629.38</v>
@@ -12399,7 +12399,7 @@
         <v>1.34793</v>
       </c>
       <c r="J178" s="15" t="n">
-        <v>33.2</v>
+        <v>15.6</v>
       </c>
       <c r="K178" s="16" t="n">
         <v>1527.68</v>
@@ -12600,7 +12600,7 @@
         <v>1.15509</v>
       </c>
       <c r="J181" s="15" t="n">
-        <v>-9.6</v>
+        <v>-10.3</v>
       </c>
       <c r="K181" s="16" t="n">
         <v>-1152.55</v>
@@ -12667,7 +12667,7 @@
         <v>0.93502</v>
       </c>
       <c r="J182" s="15" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
       </c>
       <c r="K182" s="16" t="n">
         <v>265.74</v>
@@ -12801,7 +12801,7 @@
         <v>1.35051</v>
       </c>
       <c r="J184" s="15" t="n">
-        <v>0.3</v>
+        <v>3.5</v>
       </c>
       <c r="K184" s="16" t="n">
         <v>374.54</v>
@@ -12868,7 +12868,7 @@
         <v>4385.654</v>
       </c>
       <c r="J185" s="15" t="n">
-        <v>-206.2</v>
+        <v>-206.9</v>
       </c>
       <c r="K185" s="16" t="n">
         <v>-179.34</v>
@@ -12923,7 +12923,7 @@
         <v>4.869</v>
       </c>
       <c r="F186" s="14" t="n">
-        <v>1.88188</v>
+        <v>1.88187</v>
       </c>
       <c r="G186" s="14" t="n">
         <v>1.88396</v>
@@ -12935,7 +12935,7 @@
         <v>1.88179</v>
       </c>
       <c r="J186" s="15" t="n">
-        <v>0.8</v>
+        <v>9</v>
       </c>
       <c r="K186" s="16" t="n">
         <v>438.07</v>
@@ -13002,7 +13002,7 @@
         <v>114.338</v>
       </c>
       <c r="J187" s="15" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="K187" s="16" t="n">
         <v>26.84</v>
@@ -13069,7 +13069,7 @@
         <v>1.39278</v>
       </c>
       <c r="J188" s="15" t="n">
-        <v>-11.7</v>
+        <v>-12.4</v>
       </c>
       <c r="K188" s="16" t="n">
         <v>-1125.24</v>
@@ -13136,7 +13136,7 @@
         <v>1.0983</v>
       </c>
       <c r="J189" s="15" t="n">
-        <v>16.3</v>
+        <v>13.3</v>
       </c>
       <c r="K189" s="16" t="n">
         <v>881.38</v>
